--- a/data/industry_sectors.xlsx
+++ b/data/industry_sectors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6113f60f932799a7/1Evan/.eff_fron_spyder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{1E32A5FC-D97B-4C51-B2E8-B46C6AA21334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4555068-5A26-431F-AFFC-743FACB0AFBD}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{1E32A5FC-D97B-4C51-B2E8-B46C6AA21334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02176E9E-E0A9-4451-984A-432BED44E211}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Investments" sheetId="1" r:id="rId1"/>
@@ -509,7 +509,7 @@
         <v>17</v>
       </c>
       <c r="B2" s="11">
-        <v>0.05</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="C2" s="11">
         <v>0.25</v>
@@ -523,8 +523,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C3" s="11">
-        <f>1/3</f>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -535,8 +534,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C4" s="11">
-        <f t="shared" ref="C4:C13" si="0">1/3</f>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -547,8 +545,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C5" s="11">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -559,8 +556,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C6" s="11">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -571,8 +567,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C7" s="11">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -583,8 +578,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C8" s="11">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -595,8 +589,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C9" s="11">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -607,8 +600,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C10" s="11">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -619,8 +611,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C11" s="11">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -631,8 +622,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C12" s="11">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -643,8 +633,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C13" s="11">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -679,11 +668,11 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="9">
         <f ca="1">DATE(YEAR(B2)-10,MONTH(B2),DAY(B2))</f>
-        <v>41858</v>
+        <v>41860</v>
       </c>
       <c r="B2" s="9">
         <f ca="1">NOW()-1</f>
-        <v>45511.67619583333</v>
+        <v>45513.519695138886</v>
       </c>
       <c r="C2" s="10">
         <v>5.1499999999999997E-2</v>

--- a/data/industry_sectors.xlsx
+++ b/data/industry_sectors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6113f60f932799a7/1Evan/.eff_fron_spyder/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{1E32A5FC-D97B-4C51-B2E8-B46C6AA21334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02176E9E-E0A9-4451-984A-432BED44E211}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{1E32A5FC-D97B-4C51-B2E8-B46C6AA21334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{452FBE04-0624-49AB-AEDF-EFF1C9E48A12}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -195,6 +195,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -509,10 +513,10 @@
         <v>17</v>
       </c>
       <c r="B2" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="11">
-        <v>0.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -520,10 +524,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="C3" s="11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -531,10 +535,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="C4" s="11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -542,10 +546,10 @@
         <v>8</v>
       </c>
       <c r="B5" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="C5" s="11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -553,10 +557,10 @@
         <v>9</v>
       </c>
       <c r="B6" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="C6" s="11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -564,10 +568,10 @@
         <v>10</v>
       </c>
       <c r="B7" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="C7" s="11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -575,10 +579,10 @@
         <v>11</v>
       </c>
       <c r="B8" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="C8" s="11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -586,10 +590,10 @@
         <v>12</v>
       </c>
       <c r="B9" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="C9" s="11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -597,10 +601,10 @@
         <v>13</v>
       </c>
       <c r="B10" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="C10" s="11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -608,10 +612,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="C11" s="11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -619,10 +623,10 @@
         <v>15</v>
       </c>
       <c r="B12" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="C12" s="11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -630,10 +634,10 @@
         <v>16</v>
       </c>
       <c r="B13" s="11">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="C13" s="11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -668,11 +672,11 @@
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="9">
         <f ca="1">DATE(YEAR(B2)-10,MONTH(B2),DAY(B2))</f>
-        <v>41860</v>
+        <v>41863</v>
       </c>
       <c r="B2" s="9">
         <f ca="1">NOW()-1</f>
-        <v>45513.519695138886</v>
+        <v>45516.449488541664</v>
       </c>
       <c r="C2" s="10">
         <v>5.1499999999999997E-2</v>
